--- a/output/laminas_comunales/comunal_m_movinterna_a_2023_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2023_magallanes.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: Laguna Blanca (123,9); Torres del Paine (144,5); Primavera (111,4); San Gregorio (125,8); Río Verde (129,0); Cabo de Hornos ( 93,3); Timaukel (112,3).</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_movinterna_a_2023_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2023_magallanes.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: Laguna Blanca (123,9); Torres del Paine (144,5); Primavera (111,4); San Gregorio (125,8); Río Verde (129,0); Cabo de Hornos ( 93,3); Timaukel (112,3).</t>
+          <t>Periodo 2019-2023. Escala comunal recortada a percentiles 3-97. Sobre umbral: Laguna Blanca (123,9); Torres del Paine (144,5); Primavera (111,4); San Gregorio (125,8); Río Verde (129,0); Cabo de Hornos ( 93,3); y 1 más.</t>
         </is>
       </c>
     </row>
